--- a/docs/schema/glassbox_schema.xlsx
+++ b/docs/schema/glassbox_schema.xlsx
@@ -16,7 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjuster" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClaimVendorAssignment" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StateRule" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1004,6 +1005,398 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>StateRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Logical column names shown · physical names use gbx_ prefix (Dataverse)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Column (logical)</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Physical (Dataverse)</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Choice / Default</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Lookup →</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>gbx_state_rule_id</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Auto-number</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>SR-{###}</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Primary key — one row per state</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>gbx_state</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>US 50 states + DC</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr"/>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>ISO 3166-2 state code</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>closure_deadline_days</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>gbx_closure_deadline_days</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Whole number</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>30 default</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>State-mandated claim closure window (30-45 days) — read by Notification Agent (intake_data_spec §5.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>is_no_fault</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>gbx_is_no_fault</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Yes/No</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="11" t="inlineStr"/>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>FL / NY / NJ / MI / PA / KY / KS / ND / HI / UT / OR / MA = true</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>comparative_negligence_rule</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>gbx_comp_neg_rule</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Pure|Modified50|Modified51|Contributory</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr"/>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>Pure (CA/NY/FL/MO) · Mod50 (TX/CO/GA/SC) · Mod51 (OH/MI/PA/NJ) · Contributory (MD/VA/NC/DC/AL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>um_grace_period_days</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>gbx_um_grace_days</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Whole number</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Hit-and-run police report deadline (24 / 48 / 72 hours by state)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>policy_lapse_grace_days</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>gbx_lapse_grace_days</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Whole number</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>15 default</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr"/>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Cancellation grace period 10-30 days by state — used by §1.5 gate check #2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>total_loss_threshold_pct</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>gbx_tl_threshold_pct</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>75 default</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr"/>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Repair-vs-ACV cutoff (most 75-80% · Iowa 100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>acknowledgment_deadline_days</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>gbx_ack_deadline_days</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Whole number</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>10 default</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr"/>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>FNOL acknowledgment deadline (most states 10 business days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>glass_zero_deductible</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>gbx_glass_zero_ded</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Yes/No</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr"/>
+      <c r="F14" s="11" t="inlineStr"/>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>FL / KY / KS / MA / SC / MN waive comprehensive deductible for glass-only claims</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1888,7 +2281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2845,6 +3238,126 @@
       <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>docs_outstanding</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>gbx_docs_outstanding</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Yes/No</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr"/>
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Track B flag — minimum FNOL complete but supporting docs missing (intake_data_spec §5.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>manual_contact_flag</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>gbx_manual_contact_flag</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Yes/No</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Set Y at Day 10 of post-FNOL chase when adjuster makes manual contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>chase_day_count</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>gbx_chase_day_count</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Whole number</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Days elapsed since Day 0 of post-FNOL chase cadence (intake_data_spec §5.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>legacy_claim_id</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>gbx_legacy_claim_id</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Text(50)</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Claim # assigned by legacy core after ADF push (intake_data_spec §0.5)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3275,7 +3788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3623,6 +4136,39 @@
       <c r="E14" s="7" t="inlineStr"/>
       <c r="F14" s="7" t="inlineStr"/>
       <c r="G14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>delivery_status</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>gbx_delivery_status</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Sent|Delivered|Read|Failed|Bounced</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Outbound delivery state from ACS / Outlook / Bot Service (intake_data_spec §5.5)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
